--- a/artfynd/A 9110-2025 artfynd.xlsx
+++ b/artfynd/A 9110-2025 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126363981</v>
+        <v>126362752</v>
       </c>
       <c r="B4" t="n">
-        <v>91256</v>
+        <v>77941</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,37 +898,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562269</v>
+        <v>562539</v>
       </c>
       <c r="R4" t="n">
-        <v>7306476</v>
+        <v>7307116</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,13 +966,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog vid bäckdråg</t>
+          <t>Luckig naturskog/gransumpskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -993,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126362752</v>
+        <v>126363981</v>
       </c>
       <c r="B5" t="n">
-        <v>77941</v>
+        <v>91256</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,34 +1000,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>314</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562539</v>
+        <v>562269</v>
       </c>
       <c r="R5" t="n">
-        <v>7307116</v>
+        <v>7306476</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,12 +1071,13 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Luckig naturskog/gransumpskog</t>
+          <t>Bördig grannaturskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1197,48 +1197,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126364314</v>
+        <v>126362136</v>
       </c>
       <c r="B7" t="n">
-        <v>91696</v>
+        <v>91260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
+          <t>Djupfors, Djupfors, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562054</v>
+        <v>562540</v>
       </c>
       <c r="R7" t="n">
-        <v>7306529</v>
+        <v>7307412</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1279,7 +1276,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1303,45 +1299,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126363168</v>
+        <v>126364314</v>
       </c>
       <c r="B8" t="n">
-        <v>56839</v>
+        <v>91696</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562522</v>
+        <v>562054</v>
       </c>
       <c r="R8" t="n">
-        <v>7306905</v>
+        <v>7306529</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,12 +1381,13 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Luckig naturskog/gransumpskog</t>
+          <t>Bördig grannaturskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1507,10 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126362136</v>
+        <v>126363168</v>
       </c>
       <c r="B10" t="n">
-        <v>91260</v>
+        <v>56839</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1518,34 +1518,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Djupfors, Djupfors, Ly lm</t>
+          <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562540</v>
+        <v>562522</v>
       </c>
       <c r="R10" t="n">
-        <v>7307412</v>
+        <v>7306905</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog vid bäckdråg</t>
+          <t>Luckig naturskog/gransumpskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2226,45 +2226,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126363006</v>
+        <v>126364194</v>
       </c>
       <c r="B17" t="n">
-        <v>91538</v>
+        <v>92029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>918</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562505</v>
+        <v>562123</v>
       </c>
       <c r="R17" t="n">
-        <v>7306983</v>
+        <v>7306521</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2305,12 +2308,13 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Luckig naturskog/gransumpskog</t>
+          <t>Bördig grannaturskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2328,48 +2332,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126364194</v>
+        <v>126363006</v>
       </c>
       <c r="B18" t="n">
-        <v>92029</v>
+        <v>91538</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>918</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562123</v>
+        <v>562505</v>
       </c>
       <c r="R18" t="n">
-        <v>7306521</v>
+        <v>7306983</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2410,13 +2411,12 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog vid bäckdråg</t>
+          <t>Luckig naturskog/gransumpskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2642,45 +2642,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126363110</v>
+        <v>126364128</v>
       </c>
       <c r="B21" t="n">
-        <v>91256</v>
+        <v>91696</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562533</v>
+        <v>562137</v>
       </c>
       <c r="R21" t="n">
-        <v>7306946</v>
+        <v>7306516</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2721,12 +2724,13 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Luckig naturskog/gransumpskog</t>
+          <t>Bördig grannaturskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2744,48 +2748,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126364128</v>
+        <v>126363110</v>
       </c>
       <c r="B22" t="n">
-        <v>91696</v>
+        <v>91256</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562137</v>
+        <v>562533</v>
       </c>
       <c r="R22" t="n">
-        <v>7306516</v>
+        <v>7306946</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2826,13 +2827,12 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog vid bäckdråg</t>
+          <t>Luckig naturskog/gransumpskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>

--- a/artfynd/A 9110-2025 artfynd.xlsx
+++ b/artfynd/A 9110-2025 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126362752</v>
+        <v>126363981</v>
       </c>
       <c r="B4" t="n">
-        <v>77941</v>
+        <v>91256</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,34 +898,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>314</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562539</v>
+        <v>562269</v>
       </c>
       <c r="R4" t="n">
-        <v>7307116</v>
+        <v>7306476</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,12 +969,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Luckig naturskog/gransumpskog</t>
+          <t>Bördig grannaturskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -989,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126363981</v>
+        <v>126362752</v>
       </c>
       <c r="B5" t="n">
-        <v>91256</v>
+        <v>77941</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,37 +1004,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562269</v>
+        <v>562539</v>
       </c>
       <c r="R5" t="n">
-        <v>7306476</v>
+        <v>7307116</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,13 +1072,12 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog vid bäckdråg</t>
+          <t>Luckig naturskog/gransumpskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1197,45 +1197,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126362136</v>
+        <v>126364314</v>
       </c>
       <c r="B7" t="n">
-        <v>91260</v>
+        <v>91696</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Djupfors, Djupfors, Ly lm</t>
+          <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562540</v>
+        <v>562054</v>
       </c>
       <c r="R7" t="n">
-        <v>7307412</v>
+        <v>7306529</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,6 +1279,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1299,48 +1303,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126364314</v>
+        <v>126362136</v>
       </c>
       <c r="B8" t="n">
-        <v>91696</v>
+        <v>91260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
+          <t>Djupfors, Djupfors, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562054</v>
+        <v>562540</v>
       </c>
       <c r="R8" t="n">
-        <v>7306529</v>
+        <v>7307412</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1381,7 +1382,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9110-2025 artfynd.xlsx
+++ b/artfynd/A 9110-2025 artfynd.xlsx
@@ -2022,32 +2022,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126362085</v>
+        <v>126362027</v>
       </c>
       <c r="B15" t="n">
-        <v>75063</v>
+        <v>91238</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>492</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562586</v>
+        <v>562615</v>
       </c>
       <c r="R15" t="n">
-        <v>7307426</v>
+        <v>7307464</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2124,32 +2124,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126362027</v>
+        <v>126362085</v>
       </c>
       <c r="B16" t="n">
-        <v>91238</v>
+        <v>75063</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>492</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2159,10 +2159,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562615</v>
+        <v>562586</v>
       </c>
       <c r="R16" t="n">
-        <v>7307464</v>
+        <v>7307426</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 9110-2025 artfynd.xlsx
+++ b/artfynd/A 9110-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126363508</v>
       </c>
       <c r="B2" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126363853</v>
       </c>
       <c r="B3" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126363981</v>
+        <v>126362752</v>
       </c>
       <c r="B4" t="n">
-        <v>91256</v>
+        <v>77944</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,37 +898,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562269</v>
+        <v>562539</v>
       </c>
       <c r="R4" t="n">
-        <v>7306476</v>
+        <v>7307116</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,13 +966,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog vid bäckdråg</t>
+          <t>Luckig naturskog/gransumpskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -993,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126362752</v>
+        <v>126363981</v>
       </c>
       <c r="B5" t="n">
-        <v>77941</v>
+        <v>91259</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,34 +1000,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>314</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562539</v>
+        <v>562269</v>
       </c>
       <c r="R5" t="n">
-        <v>7307116</v>
+        <v>7306476</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,12 +1071,13 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Luckig naturskog/gransumpskog</t>
+          <t>Bördig grannaturskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
         <v>126362099</v>
       </c>
       <c r="B6" t="n">
-        <v>75064</v>
+        <v>75067</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,48 +1197,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126364314</v>
+        <v>126363168</v>
       </c>
       <c r="B7" t="n">
-        <v>91696</v>
+        <v>56840</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562054</v>
+        <v>562522</v>
       </c>
       <c r="R7" t="n">
-        <v>7306529</v>
+        <v>7306905</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1279,13 +1276,12 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog vid bäckdråg</t>
+          <t>Luckig naturskog/gransumpskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1303,10 +1299,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126362136</v>
+        <v>126362161</v>
       </c>
       <c r="B8" t="n">
-        <v>91260</v>
+        <v>91541</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1314,21 +1310,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1338,10 +1334,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562540</v>
+        <v>562524</v>
       </c>
       <c r="R8" t="n">
-        <v>7307412</v>
+        <v>7307402</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,45 +1401,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126362161</v>
+        <v>126364314</v>
       </c>
       <c r="B9" t="n">
-        <v>91538</v>
+        <v>91699</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Djupfors, Djupfors, Ly lm</t>
+          <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562524</v>
+        <v>562054</v>
       </c>
       <c r="R9" t="n">
-        <v>7307402</v>
+        <v>7306529</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1484,6 +1483,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1507,10 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126363168</v>
+        <v>126362136</v>
       </c>
       <c r="B10" t="n">
-        <v>56839</v>
+        <v>91263</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1518,34 +1518,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
+          <t>Djupfors, Djupfors, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562522</v>
+        <v>562540</v>
       </c>
       <c r="R10" t="n">
-        <v>7306905</v>
+        <v>7307412</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Luckig naturskog/gransumpskog</t>
+          <t>Bördig grannaturskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1609,10 +1609,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126362288</v>
+        <v>126362607</v>
       </c>
       <c r="B11" t="n">
-        <v>78977</v>
+        <v>79059</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1620,21 +1620,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562516</v>
+        <v>562563</v>
       </c>
       <c r="R11" t="n">
-        <v>7307380</v>
+        <v>7307204</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,6 +1690,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Luckig naturskog/gransumpskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1706,10 +1711,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126362607</v>
+        <v>126362288</v>
       </c>
       <c r="B12" t="n">
-        <v>79056</v>
+        <v>78980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1717,21 +1722,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1741,10 +1746,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562563</v>
+        <v>562516</v>
       </c>
       <c r="R12" t="n">
-        <v>7307204</v>
+        <v>7307380</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1787,11 +1792,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Luckig naturskog/gransumpskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1811,7 +1811,7 @@
         <v>126364444</v>
       </c>
       <c r="B13" t="n">
-        <v>41473</v>
+        <v>41474</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>126363862</v>
       </c>
       <c r="B14" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2022,32 +2022,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126362027</v>
+        <v>126362085</v>
       </c>
       <c r="B15" t="n">
-        <v>91238</v>
+        <v>75066</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>492</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562615</v>
+        <v>562586</v>
       </c>
       <c r="R15" t="n">
-        <v>7307464</v>
+        <v>7307426</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2124,32 +2124,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126362085</v>
+        <v>126362027</v>
       </c>
       <c r="B16" t="n">
-        <v>75063</v>
+        <v>91241</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>492</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2159,10 +2159,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562586</v>
+        <v>562615</v>
       </c>
       <c r="R16" t="n">
-        <v>7307426</v>
+        <v>7307464</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2226,48 +2226,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126364194</v>
+        <v>126363006</v>
       </c>
       <c r="B17" t="n">
-        <v>92029</v>
+        <v>91541</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>918</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562123</v>
+        <v>562505</v>
       </c>
       <c r="R17" t="n">
-        <v>7306521</v>
+        <v>7306983</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2308,13 +2305,12 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog vid bäckdråg</t>
+          <t>Luckig naturskog/gransumpskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2332,45 +2328,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126363006</v>
+        <v>126364194</v>
       </c>
       <c r="B18" t="n">
-        <v>91538</v>
+        <v>92032</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>918</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562505</v>
+        <v>562123</v>
       </c>
       <c r="R18" t="n">
-        <v>7306983</v>
+        <v>7306521</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2411,12 +2410,13 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Luckig naturskog/gransumpskog</t>
+          <t>Bördig grannaturskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2437,7 +2437,7 @@
         <v>126363950</v>
       </c>
       <c r="B19" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>126362706</v>
       </c>
       <c r="B20" t="n">
-        <v>75072</v>
+        <v>75075</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>126364128</v>
       </c>
       <c r="B21" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>126363110</v>
       </c>
       <c r="B22" t="n">
-        <v>91256</v>
+        <v>91259</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 9110-2025 artfynd.xlsx
+++ b/artfynd/A 9110-2025 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126362752</v>
+        <v>126363981</v>
       </c>
       <c r="B4" t="n">
-        <v>77944</v>
+        <v>91259</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,34 +898,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>314</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562539</v>
+        <v>562269</v>
       </c>
       <c r="R4" t="n">
-        <v>7307116</v>
+        <v>7306476</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,12 +969,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Luckig naturskog/gransumpskog</t>
+          <t>Bördig grannaturskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -989,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126363981</v>
+        <v>126362752</v>
       </c>
       <c r="B5" t="n">
-        <v>91259</v>
+        <v>77944</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,37 +1004,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562269</v>
+        <v>562539</v>
       </c>
       <c r="R5" t="n">
-        <v>7306476</v>
+        <v>7307116</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,13 +1072,12 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog vid bäckdråg</t>
+          <t>Luckig naturskog/gransumpskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 9110-2025 artfynd.xlsx
+++ b/artfynd/A 9110-2025 artfynd.xlsx
@@ -1197,10 +1197,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126363168</v>
+        <v>126362161</v>
       </c>
       <c r="B7" t="n">
-        <v>56840</v>
+        <v>91541</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1208,34 +1208,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
+          <t>Djupfors, Djupfors, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562522</v>
+        <v>562524</v>
       </c>
       <c r="R7" t="n">
-        <v>7306905</v>
+        <v>7307402</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Luckig naturskog/gransumpskog</t>
+          <t>Bördig grannaturskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1299,10 +1299,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126362161</v>
+        <v>126362136</v>
       </c>
       <c r="B8" t="n">
-        <v>91541</v>
+        <v>91263</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1310,21 +1310,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1334,10 +1334,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562524</v>
+        <v>562540</v>
       </c>
       <c r="R8" t="n">
-        <v>7307402</v>
+        <v>7307412</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1507,10 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126362136</v>
+        <v>126363168</v>
       </c>
       <c r="B10" t="n">
-        <v>91263</v>
+        <v>56840</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1518,34 +1518,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Djupfors, Djupfors, Ly lm</t>
+          <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562540</v>
+        <v>562522</v>
       </c>
       <c r="R10" t="n">
-        <v>7307412</v>
+        <v>7306905</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog vid bäckdråg</t>
+          <t>Luckig naturskog/gransumpskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1609,10 +1609,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126362607</v>
+        <v>126362288</v>
       </c>
       <c r="B11" t="n">
-        <v>79059</v>
+        <v>78980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1620,21 +1620,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562563</v>
+        <v>562516</v>
       </c>
       <c r="R11" t="n">
-        <v>7307204</v>
+        <v>7307380</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,11 +1690,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Luckig naturskog/gransumpskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1711,10 +1706,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126362288</v>
+        <v>126362607</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>79059</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1722,21 +1717,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1746,10 +1741,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562516</v>
+        <v>562563</v>
       </c>
       <c r="R12" t="n">
-        <v>7307380</v>
+        <v>7307204</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1792,6 +1787,11 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Luckig naturskog/gransumpskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2226,45 +2226,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126363006</v>
+        <v>126364194</v>
       </c>
       <c r="B17" t="n">
-        <v>91541</v>
+        <v>92032</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>918</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562505</v>
+        <v>562123</v>
       </c>
       <c r="R17" t="n">
-        <v>7306983</v>
+        <v>7306521</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2305,12 +2308,13 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Luckig naturskog/gransumpskog</t>
+          <t>Bördig grannaturskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2328,48 +2332,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126364194</v>
+        <v>126363006</v>
       </c>
       <c r="B18" t="n">
-        <v>92032</v>
+        <v>91541</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>918</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562123</v>
+        <v>562505</v>
       </c>
       <c r="R18" t="n">
-        <v>7306521</v>
+        <v>7306983</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2410,13 +2411,12 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog vid bäckdråg</t>
+          <t>Luckig naturskog/gransumpskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 9110-2025 artfynd.xlsx
+++ b/artfynd/A 9110-2025 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126363981</v>
+        <v>126362752</v>
       </c>
       <c r="B4" t="n">
-        <v>91259</v>
+        <v>77944</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,37 +898,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562269</v>
+        <v>562539</v>
       </c>
       <c r="R4" t="n">
-        <v>7306476</v>
+        <v>7307116</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,13 +966,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog vid bäckdråg</t>
+          <t>Luckig naturskog/gransumpskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -993,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126362752</v>
+        <v>126363981</v>
       </c>
       <c r="B5" t="n">
-        <v>77944</v>
+        <v>91259</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,34 +1000,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>314</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562539</v>
+        <v>562269</v>
       </c>
       <c r="R5" t="n">
-        <v>7307116</v>
+        <v>7306476</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,12 +1071,13 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Luckig naturskog/gransumpskog</t>
+          <t>Bördig grannaturskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 9110-2025 artfynd.xlsx
+++ b/artfynd/A 9110-2025 artfynd.xlsx
@@ -1299,45 +1299,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126362136</v>
+        <v>126364314</v>
       </c>
       <c r="B8" t="n">
-        <v>91263</v>
+        <v>91699</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Djupfors, Djupfors, Ly lm</t>
+          <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562540</v>
+        <v>562054</v>
       </c>
       <c r="R8" t="n">
-        <v>7307412</v>
+        <v>7306529</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,6 +1381,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1401,48 +1405,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126364314</v>
+        <v>126363168</v>
       </c>
       <c r="B9" t="n">
-        <v>91699</v>
+        <v>56840</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562054</v>
+        <v>562522</v>
       </c>
       <c r="R9" t="n">
-        <v>7306529</v>
+        <v>7306905</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1483,13 +1484,12 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog vid bäckdråg</t>
+          <t>Luckig naturskog/gransumpskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1507,10 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126363168</v>
+        <v>126362136</v>
       </c>
       <c r="B10" t="n">
-        <v>56840</v>
+        <v>91263</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1518,34 +1518,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
+          <t>Djupfors, Djupfors, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562522</v>
+        <v>562540</v>
       </c>
       <c r="R10" t="n">
-        <v>7306905</v>
+        <v>7307412</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Luckig naturskog/gransumpskog</t>
+          <t>Bördig grannaturskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1609,10 +1609,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126362288</v>
+        <v>126362607</v>
       </c>
       <c r="B11" t="n">
-        <v>78980</v>
+        <v>79059</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1620,21 +1620,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562516</v>
+        <v>562563</v>
       </c>
       <c r="R11" t="n">
-        <v>7307380</v>
+        <v>7307204</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,6 +1690,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Luckig naturskog/gransumpskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1706,10 +1711,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126362607</v>
+        <v>126362288</v>
       </c>
       <c r="B12" t="n">
-        <v>79059</v>
+        <v>78980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1717,21 +1722,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1741,10 +1746,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562563</v>
+        <v>562516</v>
       </c>
       <c r="R12" t="n">
-        <v>7307204</v>
+        <v>7307380</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1787,11 +1792,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Luckig naturskog/gransumpskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1808,10 +1808,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126364444</v>
+        <v>126363862</v>
       </c>
       <c r="B13" t="n">
-        <v>41474</v>
+        <v>91541</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1819,28 +1819,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>215698</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsfältmätare</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Xanthorhoe annotinata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Zetterstedt, 1839)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1848,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562044</v>
+        <v>562295</v>
       </c>
       <c r="R13" t="n">
-        <v>7306628</v>
+        <v>7306479</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,7 +1896,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Luckig grannaturskog</t>
+          <t>Bördig grannaturskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1916,48 +1914,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126363862</v>
+        <v>126362085</v>
       </c>
       <c r="B14" t="n">
-        <v>91541</v>
+        <v>75066</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>492</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
+          <t>Djupfors, Djupfors, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562295</v>
+        <v>562586</v>
       </c>
       <c r="R14" t="n">
-        <v>7306479</v>
+        <v>7307426</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,7 +1993,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2022,32 +2016,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126362085</v>
+        <v>126362027</v>
       </c>
       <c r="B15" t="n">
-        <v>75066</v>
+        <v>91241</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>492</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2057,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562586</v>
+        <v>562615</v>
       </c>
       <c r="R15" t="n">
-        <v>7307426</v>
+        <v>7307464</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2124,45 +2118,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126362027</v>
+        <v>126364194</v>
       </c>
       <c r="B16" t="n">
-        <v>91241</v>
+        <v>92032</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>918</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Djupfors, Djupfors, Ly lm</t>
+          <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562615</v>
+        <v>562123</v>
       </c>
       <c r="R16" t="n">
-        <v>7307464</v>
+        <v>7306521</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2203,6 +2200,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2226,48 +2224,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126364194</v>
+        <v>126363006</v>
       </c>
       <c r="B17" t="n">
-        <v>92032</v>
+        <v>91541</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>918</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562123</v>
+        <v>562505</v>
       </c>
       <c r="R17" t="n">
-        <v>7306521</v>
+        <v>7306983</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2308,13 +2303,12 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog vid bäckdråg</t>
+          <t>Luckig naturskog/gransumpskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2332,10 +2326,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126363006</v>
+        <v>126363950</v>
       </c>
       <c r="B18" t="n">
-        <v>91541</v>
+        <v>91245</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2343,34 +2337,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562505</v>
+        <v>562262</v>
       </c>
       <c r="R18" t="n">
-        <v>7306983</v>
+        <v>7306451</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2411,12 +2408,13 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Luckig naturskog/gransumpskog</t>
+          <t>Bördig grannaturskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2434,10 +2432,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126363950</v>
+        <v>126362706</v>
       </c>
       <c r="B19" t="n">
-        <v>91245</v>
+        <v>75075</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2445,37 +2443,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562262</v>
+        <v>562562</v>
       </c>
       <c r="R19" t="n">
-        <v>7306451</v>
+        <v>7307134</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2516,13 +2511,12 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog vid bäckdråg</t>
+          <t>Luckig naturskog/gransumpskog</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2540,45 +2534,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126362706</v>
+        <v>126364128</v>
       </c>
       <c r="B20" t="n">
-        <v>75075</v>
+        <v>91699</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562562</v>
+        <v>562137</v>
       </c>
       <c r="R20" t="n">
-        <v>7307134</v>
+        <v>7306516</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2619,12 +2616,13 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Luckig naturskog/gransumpskog</t>
+          <t>Bördig grannaturskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2642,48 +2640,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126364128</v>
+        <v>126363110</v>
       </c>
       <c r="B21" t="n">
-        <v>91699</v>
+        <v>91259</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562137</v>
+        <v>562533</v>
       </c>
       <c r="R21" t="n">
-        <v>7306516</v>
+        <v>7306946</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2724,13 +2719,12 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog vid bäckdråg</t>
+          <t>Luckig naturskog/gransumpskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2748,10 +2742,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126363110</v>
+        <v>126364444</v>
       </c>
       <c r="B22" t="n">
-        <v>91259</v>
+        <v>41474</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2759,34 +2753,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1204</v>
+        <v>215698</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skogsfältmätare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Xanthorhoe annotinata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Zetterstedt, 1839)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562533</v>
+        <v>562044</v>
       </c>
       <c r="R22" t="n">
-        <v>7306946</v>
+        <v>7306628</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2827,12 +2826,13 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Luckig naturskog/gransumpskog</t>
+          <t>Luckig grannaturskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>

--- a/artfynd/A 9110-2025 artfynd.xlsx
+++ b/artfynd/A 9110-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126363508</v>
+        <v>126362099</v>
       </c>
       <c r="B2" t="n">
-        <v>91541</v>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
+          <t>Djupfors, Djupfors, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562410</v>
+        <v>562586</v>
       </c>
       <c r="R2" t="n">
-        <v>7306695</v>
+        <v>7307426</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126363853</v>
+        <v>126362752</v>
       </c>
       <c r="B3" t="n">
-        <v>91699</v>
+        <v>78350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,37 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562295</v>
+        <v>562539</v>
       </c>
       <c r="R3" t="n">
-        <v>7306479</v>
+        <v>7307116</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,13 +856,12 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog vid bäckdråg</t>
+          <t>Luckig naturskog/gransumpskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -887,45 +879,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126362752</v>
+        <v>126362085</v>
       </c>
       <c r="B4" t="n">
-        <v>77944</v>
+        <v>83298</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>314</v>
+        <v>492</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
+          <t>Djupfors, Djupfors, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562539</v>
+        <v>562586</v>
       </c>
       <c r="R4" t="n">
-        <v>7307116</v>
+        <v>7307426</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +963,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Luckig naturskog/gransumpskog</t>
+          <t>Bördig grannaturskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -989,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126363981</v>
+        <v>126362161</v>
       </c>
       <c r="B5" t="n">
-        <v>91259</v>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,37 +992,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
+          <t>Djupfors, Djupfors, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562269</v>
+        <v>562524</v>
       </c>
       <c r="R5" t="n">
-        <v>7306476</v>
+        <v>7307402</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1060,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1095,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126362099</v>
+        <v>126363006</v>
       </c>
       <c r="B6" t="n">
-        <v>75067</v>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,34 +1094,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>308</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Djupfors, Djupfors, Ly lm</t>
+          <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562586</v>
+        <v>562505</v>
       </c>
       <c r="R6" t="n">
-        <v>7307426</v>
+        <v>7306983</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,7 +1167,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog vid bäckdråg</t>
+          <t>Luckig naturskog/gransumpskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1197,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126362161</v>
+        <v>126363508</v>
       </c>
       <c r="B7" t="n">
-        <v>91541</v>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1217,25 +1205,28 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Djupfors, Djupfors, Ly lm</t>
+          <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562524</v>
+        <v>562410</v>
       </c>
       <c r="R7" t="n">
-        <v>7307402</v>
+        <v>7306695</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,6 +1267,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1299,32 +1291,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126364314</v>
+        <v>126363862</v>
       </c>
       <c r="B8" t="n">
-        <v>91699</v>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1329,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562054</v>
+        <v>562295</v>
       </c>
       <c r="R8" t="n">
-        <v>7306529</v>
+        <v>7306479</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,10 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126363168</v>
+        <v>126362607</v>
       </c>
       <c r="B9" t="n">
-        <v>56840</v>
+        <v>79406</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1416,34 +1408,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>864</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
+          <t>Djupfors, Djupfors, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562522</v>
+        <v>562563</v>
       </c>
       <c r="R9" t="n">
-        <v>7306905</v>
+        <v>7307204</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1507,45 +1499,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126362136</v>
+        <v>126364194</v>
       </c>
       <c r="B10" t="n">
-        <v>91263</v>
+        <v>92721</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>918</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Djupfors, Djupfors, Ly lm</t>
+          <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562540</v>
+        <v>562123</v>
       </c>
       <c r="R10" t="n">
-        <v>7307412</v>
+        <v>7306521</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1586,6 +1581,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1609,10 +1605,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126362288</v>
+        <v>126362027</v>
       </c>
       <c r="B11" t="n">
-        <v>78980</v>
+        <v>91905</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1620,21 +1616,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1644,10 +1640,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562516</v>
+        <v>562615</v>
       </c>
       <c r="R11" t="n">
-        <v>7307380</v>
+        <v>7307464</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,6 +1686,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Bördig grannaturskog vid bäckdråg</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1706,10 +1707,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126362607</v>
+        <v>126363950</v>
       </c>
       <c r="B12" t="n">
-        <v>79059</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1717,34 +1718,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Djupfors, Djupfors, Ly lm</t>
+          <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562563</v>
+        <v>562262</v>
       </c>
       <c r="R12" t="n">
-        <v>7307204</v>
+        <v>7306451</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1785,12 +1789,13 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Luckig naturskog/gransumpskog</t>
+          <t>Bördig grannaturskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1808,48 +1813,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126363862</v>
+        <v>126363110</v>
       </c>
       <c r="B13" t="n">
-        <v>91541</v>
+        <v>91923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562295</v>
+        <v>562533</v>
       </c>
       <c r="R13" t="n">
-        <v>7306479</v>
+        <v>7306946</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1890,13 +1892,12 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog vid bäckdråg</t>
+          <t>Luckig naturskog/gransumpskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1914,10 +1915,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126362085</v>
+        <v>126363981</v>
       </c>
       <c r="B14" t="n">
-        <v>75066</v>
+        <v>91923</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1925,34 +1926,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>492</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Djupfors, Djupfors, Ly lm</t>
+          <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562586</v>
+        <v>562269</v>
       </c>
       <c r="R14" t="n">
-        <v>7307426</v>
+        <v>7306476</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1993,6 +1997,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2016,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126362027</v>
+        <v>126363853</v>
       </c>
       <c r="B15" t="n">
-        <v>91241</v>
+        <v>92369</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2027,34 +2032,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Djupfors, Djupfors, Ly lm</t>
+          <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562615</v>
+        <v>562295</v>
       </c>
       <c r="R15" t="n">
-        <v>7307464</v>
+        <v>7306479</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2095,6 +2103,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2118,32 +2127,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126364194</v>
+        <v>126364128</v>
       </c>
       <c r="B16" t="n">
-        <v>92032</v>
+        <v>92369</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>918</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2156,10 +2165,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562123</v>
+        <v>562137</v>
       </c>
       <c r="R16" t="n">
-        <v>7306521</v>
+        <v>7306516</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2224,10 +2233,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126363006</v>
+        <v>126364314</v>
       </c>
       <c r="B17" t="n">
-        <v>91541</v>
+        <v>92369</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2235,34 +2244,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562505</v>
+        <v>562054</v>
       </c>
       <c r="R17" t="n">
-        <v>7306983</v>
+        <v>7306529</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2303,12 +2315,13 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Luckig naturskog/gransumpskog</t>
+          <t>Bördig grannaturskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2326,48 +2339,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126363950</v>
+        <v>126362288</v>
       </c>
       <c r="B18" t="n">
-        <v>91245</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
+          <t>Djupfors, Djupfors, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562262</v>
+        <v>562516</v>
       </c>
       <c r="R18" t="n">
-        <v>7306451</v>
+        <v>7307380</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2408,14 +2418,8 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Bördig grannaturskog vid bäckdråg</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2435,7 +2439,7 @@
         <v>126362706</v>
       </c>
       <c r="B19" t="n">
-        <v>75075</v>
+        <v>83307</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,48 +2538,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126364128</v>
+        <v>126363168</v>
       </c>
       <c r="B20" t="n">
-        <v>91699</v>
+        <v>57132</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>102612</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562137</v>
+        <v>562522</v>
       </c>
       <c r="R20" t="n">
-        <v>7306516</v>
+        <v>7306905</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2616,13 +2617,12 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Bördig grannaturskog vid bäckdråg</t>
+          <t>Luckig naturskog/gransumpskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2640,10 +2640,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126363110</v>
+        <v>126364444</v>
       </c>
       <c r="B21" t="n">
-        <v>91259</v>
+        <v>41713</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2651,34 +2651,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1204</v>
+        <v>215698</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skogsfältmätare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Xanthorhoe annotinata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Zetterstedt, 1839)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562533</v>
+        <v>562044</v>
       </c>
       <c r="R21" t="n">
-        <v>7306946</v>
+        <v>7306628</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2719,12 +2724,13 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Luckig naturskog/gransumpskog</t>
+          <t>Luckig grannaturskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2739,114 +2745,6 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>126364444</v>
-      </c>
-      <c r="B22" t="n">
-        <v>41474</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>215698</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Skogsfältmätare</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Xanthorhoe annotinata</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Zetterstedt, 1839)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Östra Fäbodbäcken, Östra Fäbodbäcken, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>562044</v>
-      </c>
-      <c r="R22" t="n">
-        <v>7306628</v>
-      </c>
-      <c r="S22" t="n">
-        <v>10</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Luckig grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9110-2025 artfynd.xlsx
+++ b/artfynd/A 9110-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126362099</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126362752</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126362085</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126362161</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126363006</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,6 +1318,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126363508</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1394,6 +1429,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126363862</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1496,6 +1536,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126362607</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1602,6 +1647,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126364194</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1704,6 +1754,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126362027</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1810,6 +1865,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126363950</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1912,6 +1972,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126363110</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2018,6 +2083,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126363981</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2124,6 +2194,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126363853</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2230,6 +2305,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126364128</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2336,6 +2416,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126364314</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2433,6 +2518,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126362288</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2535,6 +2625,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126362706</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2637,6 +2732,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126363168</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2745,8 +2845,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126364444</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>